--- a/OHC_ensemble/coverage.xlsx
+++ b/OHC_ensemble/coverage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15_codefigurestats/OHC_ensemble/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669C0160-22D6-2D4B-AC36-3E9EBA20907F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBFE5EE-4F38-F942-AB36-FA68167BA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21180" xr2:uid="{DE02F902-72F0-CD42-A7B4-E77ACE7F346F}"/>
+    <workbookView xWindow="10260" yWindow="600" windowWidth="27920" windowHeight="21180" xr2:uid="{DE02F902-72F0-CD42-A7B4-E77ACE7F346F}"/>
   </bookViews>
   <sheets>
     <sheet name="Obs" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="94">
   <si>
     <t>IAP</t>
   </si>
@@ -304,6 +304,21 @@
   </si>
   <si>
     <t>then we draw from each of the products equally weighted, including Zanna still</t>
+  </si>
+  <si>
+    <t>https://www.metoffice.gov.uk/hadobs/en4/download-en4-2-2.html</t>
+  </si>
+  <si>
+    <t>Source(s)</t>
+  </si>
+  <si>
+    <t>http://www.ocean.iap.ac.cn/ftp/images_files/IAPv4.2_OHC_estimate_update.txt</t>
+  </si>
+  <si>
+    <t>https://www.data.jma.go.jp/kaiyou/data/english/ohc/ohc_global_1955.txt</t>
+  </si>
+  <si>
+    <t>https://www.ncei.noaa.gov/access/global-ocean-heat-content/heat_global.html</t>
   </si>
 </sst>
 </file>
@@ -327,7 +342,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,6 +361,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -359,12 +380,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7506DD-4F10-6A4E-B29B-FF73C8824AF1}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -712,7 +734,7 @@
     <col min="9" max="9" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -737,8 +759,11 @@
       <c r="H1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,11 +779,14 @@
       <c r="G2">
         <v>1992</v>
       </c>
-      <c r="H2">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H2" s="5">
+        <v>2025</v>
+      </c>
+      <c r="M2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,8 +805,12 @@
       <c r="F3">
         <v>2024</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H3" s="2"/>
+      <c r="M3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -798,7 +830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -808,7 +840,7 @@
       <c r="G5">
         <v>1900</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>2025</v>
       </c>
       <c r="I5" t="s">
@@ -817,8 +849,11 @@
       <c r="J5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -835,7 +870,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -852,7 +887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -869,7 +904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -880,10 +915,14 @@
         <v>1955</v>
       </c>
       <c r="F9">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2025</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="M9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -900,7 +939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -914,7 +953,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C16" t="s">
         <v>85</v>
       </c>
